--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597851</v>
+        <v>121597854</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447943</v>
+        <v>448058</v>
       </c>
       <c r="R2" t="n">
-        <v>7094811</v>
+        <v>7094986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597853</v>
+        <v>121597846</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447952</v>
+        <v>448172</v>
       </c>
       <c r="R3" t="n">
-        <v>7094933</v>
+        <v>7094972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597847</v>
+        <v>121597849</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448177</v>
+        <v>448158</v>
       </c>
       <c r="R4" t="n">
-        <v>7094965</v>
+        <v>7094678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597846</v>
+        <v>121597853</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448172</v>
+        <v>447952</v>
       </c>
       <c r="R5" t="n">
-        <v>7094972</v>
+        <v>7094933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597849</v>
+        <v>121597845</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448158</v>
+        <v>448114</v>
       </c>
       <c r="R6" t="n">
-        <v>7094678</v>
+        <v>7095009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597852</v>
+        <v>121597847</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447967</v>
+        <v>448177</v>
       </c>
       <c r="R7" t="n">
-        <v>7094841</v>
+        <v>7094965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597845</v>
+        <v>121597851</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448114</v>
+        <v>447943</v>
       </c>
       <c r="R8" t="n">
-        <v>7095009</v>
+        <v>7094811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597854</v>
+        <v>121597852</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448058</v>
+        <v>447967</v>
       </c>
       <c r="R9" t="n">
-        <v>7094986</v>
+        <v>7094841</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597854</v>
+        <v>121597853</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448058</v>
+        <v>447952</v>
       </c>
       <c r="R2" t="n">
-        <v>7094986</v>
+        <v>7094933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597846</v>
+        <v>121597849</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448172</v>
+        <v>448158</v>
       </c>
       <c r="R3" t="n">
-        <v>7094972</v>
+        <v>7094678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597849</v>
+        <v>121597851</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448158</v>
+        <v>447943</v>
       </c>
       <c r="R4" t="n">
-        <v>7094678</v>
+        <v>7094811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597853</v>
+        <v>121597846</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447952</v>
+        <v>448172</v>
       </c>
       <c r="R5" t="n">
-        <v>7094933</v>
+        <v>7094972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597845</v>
+        <v>121597852</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448114</v>
+        <v>447967</v>
       </c>
       <c r="R6" t="n">
-        <v>7095009</v>
+        <v>7094841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597851</v>
+        <v>121597845</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447943</v>
+        <v>448114</v>
       </c>
       <c r="R8" t="n">
-        <v>7094811</v>
+        <v>7095009</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597852</v>
+        <v>121597854</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447967</v>
+        <v>448058</v>
       </c>
       <c r="R9" t="n">
-        <v>7094841</v>
+        <v>7094986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597853</v>
+        <v>121597852</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447952</v>
+        <v>447967</v>
       </c>
       <c r="R2" t="n">
-        <v>7094933</v>
+        <v>7094841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597849</v>
+        <v>121597848</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448158</v>
+        <v>448217</v>
       </c>
       <c r="R3" t="n">
-        <v>7094678</v>
+        <v>7094913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597852</v>
+        <v>121597854</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447967</v>
+        <v>448058</v>
       </c>
       <c r="R6" t="n">
-        <v>7094841</v>
+        <v>7094986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597847</v>
+        <v>121597845</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448177</v>
+        <v>448114</v>
       </c>
       <c r="R7" t="n">
-        <v>7094965</v>
+        <v>7095009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597845</v>
+        <v>121597849</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448114</v>
+        <v>448158</v>
       </c>
       <c r="R8" t="n">
-        <v>7095009</v>
+        <v>7094678</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597854</v>
+        <v>121597847</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448058</v>
+        <v>448177</v>
       </c>
       <c r="R9" t="n">
-        <v>7094986</v>
+        <v>7094965</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597848</v>
+        <v>121597853</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448217</v>
+        <v>447952</v>
       </c>
       <c r="R10" t="n">
-        <v>7094913</v>
+        <v>7094933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597852</v>
+        <v>121597845</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447967</v>
+        <v>448114</v>
       </c>
       <c r="R2" t="n">
-        <v>7094841</v>
+        <v>7095009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597848</v>
+        <v>121597854</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448217</v>
+        <v>448058</v>
       </c>
       <c r="R3" t="n">
-        <v>7094913</v>
+        <v>7094986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597851</v>
+        <v>121597849</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447943</v>
+        <v>448158</v>
       </c>
       <c r="R4" t="n">
-        <v>7094811</v>
+        <v>7094678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597846</v>
+        <v>121597852</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448172</v>
+        <v>447967</v>
       </c>
       <c r="R5" t="n">
-        <v>7094972</v>
+        <v>7094841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597854</v>
+        <v>121597853</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448058</v>
+        <v>447952</v>
       </c>
       <c r="R6" t="n">
-        <v>7094986</v>
+        <v>7094933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597845</v>
+        <v>121597846</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448114</v>
+        <v>448172</v>
       </c>
       <c r="R7" t="n">
-        <v>7095009</v>
+        <v>7094972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597849</v>
+        <v>121597848</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448158</v>
+        <v>448217</v>
       </c>
       <c r="R8" t="n">
-        <v>7094678</v>
+        <v>7094913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>121597847</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597853</v>
+        <v>121597851</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447952</v>
+        <v>447943</v>
       </c>
       <c r="R10" t="n">
-        <v>7094933</v>
+        <v>7094811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597854</v>
+        <v>121597849</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448058</v>
+        <v>448158</v>
       </c>
       <c r="R2" t="n">
-        <v>7094986</v>
+        <v>7094678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597846</v>
+        <v>121597848</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448172</v>
+        <v>448217</v>
       </c>
       <c r="R3" t="n">
-        <v>7094972</v>
+        <v>7094913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121597848</v>
+        <v>121597847</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448217</v>
+        <v>448177</v>
       </c>
       <c r="R4" t="n">
-        <v>7094913</v>
+        <v>7094965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121597849</v>
+        <v>121597852</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448158</v>
+        <v>447967</v>
       </c>
       <c r="R6" t="n">
-        <v>7094678</v>
+        <v>7094841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597845</v>
+        <v>121597854</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448114</v>
+        <v>448058</v>
       </c>
       <c r="R7" t="n">
-        <v>7095009</v>
+        <v>7094986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597852</v>
+        <v>121597845</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447967</v>
+        <v>448114</v>
       </c>
       <c r="R8" t="n">
-        <v>7094841</v>
+        <v>7095009</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597851</v>
+        <v>121597846</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447943</v>
+        <v>448172</v>
       </c>
       <c r="R9" t="n">
-        <v>7094811</v>
+        <v>7094972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597847</v>
+        <v>121597851</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448177</v>
+        <v>447943</v>
       </c>
       <c r="R10" t="n">
-        <v>7094965</v>
+        <v>7094811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52486-2024 artfynd.xlsx
+++ b/artfynd/A 52486-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597849</v>
+        <v>121597848</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448158</v>
+        <v>448217</v>
       </c>
       <c r="R2" t="n">
-        <v>7094678</v>
+        <v>7094913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597848</v>
+        <v>121597853</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448217</v>
+        <v>447952</v>
       </c>
       <c r="R3" t="n">
-        <v>7094913</v>
+        <v>7094933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121597853</v>
+        <v>121597851</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447952</v>
+        <v>447943</v>
       </c>
       <c r="R5" t="n">
-        <v>7094933</v>
+        <v>7094811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121597854</v>
+        <v>121597845</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448058</v>
+        <v>448114</v>
       </c>
       <c r="R7" t="n">
-        <v>7094986</v>
+        <v>7095009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121597845</v>
+        <v>121597846</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448114</v>
+        <v>448172</v>
       </c>
       <c r="R8" t="n">
-        <v>7095009</v>
+        <v>7094972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121597846</v>
+        <v>121597854</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448172</v>
+        <v>448058</v>
       </c>
       <c r="R9" t="n">
-        <v>7094972</v>
+        <v>7094986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121597851</v>
+        <v>121597849</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447943</v>
+        <v>448158</v>
       </c>
       <c r="R10" t="n">
-        <v>7094811</v>
+        <v>7094678</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
